--- a/inv/unisex_eyewear.xlsx
+++ b/inv/unisex_eyewear.xlsx
@@ -2,56 +2,61 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="150" windowWidth="16215" windowHeight="8970"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
   <si>
     <t>titleid</t>
   </si>
   <si>
-    <t>unisex_eyewear</t>
-  </si>
-  <si>
-    <t>unisex_stoles</t>
-  </si>
-  <si>
-    <t>Unisex Stoles</t>
-  </si>
-  <si>
-    <t>Unisex Eye Wear</t>
-  </si>
-  <si>
-    <t>Unisex Mobile Cases</t>
-  </si>
-  <si>
-    <t>unisex_mobilecases</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>scat</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>unisex_eyewear_sunglasses</t>
+  </si>
+  <si>
+    <t>Sun Glasses</t>
+  </si>
+  <si>
+    <t>?page=unisex_eyewear_sunglasses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -76,13 +81,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -370,61 +375,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>